--- a/fixtures/ficticios/siddex/fabricantes.xlsx
+++ b/fixtures/ficticios/siddex/fabricantes.xlsx
@@ -448,7 +448,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>134.000.842</t>
+          <t>900.000.842</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -456,7 +456,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PVCC550942</t>
+          <t>FXT9550942</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -468,7 +468,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I33.000.786</t>
+          <t>Z33.000.786</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -508,7 +508,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MO01001</t>
+          <t>SV09001</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -516,12 +516,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MO01001</t>
+          <t>SV09001</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SERVICIO TURISMO (CONTRATOS)</t>
+          <t>SERVICIO FICTICIO (CONTRATOS)</t>
         </is>
       </c>
     </row>
